--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAAB7989-A69D-4CC8-BEDC-81CED190FED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF32D09-5F9A-4025-A359-A730D35086FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5652"/>
+  <dimension ref="A1:E5653"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96541,6 +96541,23 @@
         <v>2016</v>
       </c>
     </row>
+    <row r="5653" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5653">
+        <v>615126</v>
+      </c>
+      <c r="B5653">
+        <v>20260701</v>
+      </c>
+      <c r="C5653" s="1">
+        <v>902</v>
+      </c>
+      <c r="D5653" s="1">
+        <v>4816</v>
+      </c>
+      <c r="E5653" s="1">
+        <v>8240</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF32D09-5F9A-4025-A359-A730D35086FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582EC38E-2EA4-49C0-933B-3CFD980D620B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5653"/>
+  <dimension ref="A1:E5654"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96558,6 +96558,23 @@
         <v>8240</v>
       </c>
     </row>
+    <row r="5654" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5654">
+        <v>615226</v>
+      </c>
+      <c r="B5654">
+        <v>20260704</v>
+      </c>
+      <c r="C5654" s="1">
+        <v>1995</v>
+      </c>
+      <c r="D5654" s="1">
+        <v>3628</v>
+      </c>
+      <c r="E5654" s="1">
+        <v>2126</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582EC38E-2EA4-49C0-933B-3CFD980D620B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FCBD19-13F1-4866-8760-CF1FB913BC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5654"/>
+  <dimension ref="A1:E5655"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96575,6 +96575,23 @@
         <v>2126</v>
       </c>
     </row>
+    <row r="5655" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5655">
+        <v>615326</v>
+      </c>
+      <c r="B5655">
+        <v>20260705</v>
+      </c>
+      <c r="C5655" s="1">
+        <v>8681</v>
+      </c>
+      <c r="D5655" s="1">
+        <v>1582</v>
+      </c>
+      <c r="E5655" s="1">
+        <v>9926</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FCBD19-13F1-4866-8760-CF1FB913BC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FDFE4A-1509-486F-AB70-6B6EAC37EBF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5655"/>
+  <dimension ref="A1:E5656"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96592,6 +96592,23 @@
         <v>9926</v>
       </c>
     </row>
+    <row r="5656" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5656">
+        <v>615426</v>
+      </c>
+      <c r="B5656">
+        <v>20260708</v>
+      </c>
+      <c r="C5656" s="1">
+        <v>8684</v>
+      </c>
+      <c r="D5656" s="1">
+        <v>8276</v>
+      </c>
+      <c r="E5656" s="1">
+        <v>9578</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FDFE4A-1509-486F-AB70-6B6EAC37EBF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0584D90-7EE5-4E71-8D47-A5DEBE78CF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5656"/>
+  <dimension ref="A1:E5657"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96609,6 +96609,23 @@
         <v>9578</v>
       </c>
     </row>
+    <row r="5657" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5657">
+        <v>615526</v>
+      </c>
+      <c r="B5657">
+        <v>20260711</v>
+      </c>
+      <c r="C5657" s="1">
+        <v>4943</v>
+      </c>
+      <c r="D5657" s="1">
+        <v>9115</v>
+      </c>
+      <c r="E5657" s="1">
+        <v>8613</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0584D90-7EE5-4E71-8D47-A5DEBE78CF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FBC55A6-53D6-4CAD-8FCA-27C0F9C90A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5657"/>
+  <dimension ref="A1:E5658"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96626,6 +96626,23 @@
         <v>8613</v>
       </c>
     </row>
+    <row r="5658" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5658">
+        <v>615626</v>
+      </c>
+      <c r="B5658">
+        <v>20260712</v>
+      </c>
+      <c r="C5658" s="1">
+        <v>6485</v>
+      </c>
+      <c r="D5658" s="1">
+        <v>4994</v>
+      </c>
+      <c r="E5658" s="1">
+        <v>4965</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FBC55A6-53D6-4CAD-8FCA-27C0F9C90A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{440699D4-FFA4-47B1-AD71-EB27D843CEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5658"/>
+  <dimension ref="A1:E5659"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96643,6 +96643,23 @@
         <v>4965</v>
       </c>
     </row>
+    <row r="5659" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5659">
+        <v>615726</v>
+      </c>
+      <c r="B5659">
+        <v>20260715</v>
+      </c>
+      <c r="C5659" s="1">
+        <v>4175</v>
+      </c>
+      <c r="D5659" s="1">
+        <v>3196</v>
+      </c>
+      <c r="E5659" s="1">
+        <v>9328</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{440699D4-FFA4-47B1-AD71-EB27D843CEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818B55BC-9B25-495D-8ACD-8EB3FD213EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5659"/>
+  <dimension ref="A1:E5660"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96660,6 +96660,23 @@
         <v>9328</v>
       </c>
     </row>
+    <row r="5660" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5660">
+        <v>615826</v>
+      </c>
+      <c r="B5660">
+        <v>20260718</v>
+      </c>
+      <c r="C5660" s="1">
+        <v>4132</v>
+      </c>
+      <c r="D5660" s="1">
+        <v>8072</v>
+      </c>
+      <c r="E5660" s="1">
+        <v>4724</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818B55BC-9B25-495D-8ACD-8EB3FD213EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553F74AF-89D7-4066-86CB-FDB5A18037E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <definedName name="_4D" localSheetId="0">Sheet1!$A$1:$E$5652</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -447,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5660"/>
+  <dimension ref="A1:E5661"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96677,6 +96678,23 @@
         <v>4724</v>
       </c>
     </row>
+    <row r="5661" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5661">
+        <v>615926</v>
+      </c>
+      <c r="B5661">
+        <v>20260719</v>
+      </c>
+      <c r="C5661" s="1">
+        <v>1181</v>
+      </c>
+      <c r="D5661" s="1">
+        <v>9327</v>
+      </c>
+      <c r="E5661" s="1">
+        <v>3281</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553F74AF-89D7-4066-86CB-FDB5A18037E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA3156E-145D-4036-A558-CCC32DDDDDC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <definedName name="_4D" localSheetId="0">Sheet1!$A$1:$E$5652</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -448,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5661"/>
+  <dimension ref="A1:E5662"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96695,6 +96694,23 @@
         <v>3281</v>
       </c>
     </row>
+    <row r="5662" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5662">
+        <v>616026</v>
+      </c>
+      <c r="B5662">
+        <v>20260722</v>
+      </c>
+      <c r="C5662" s="1">
+        <v>2380</v>
+      </c>
+      <c r="D5662" s="1">
+        <v>5670</v>
+      </c>
+      <c r="E5662" s="1">
+        <v>2264</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA3156E-145D-4036-A558-CCC32DDDDDC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E35194D-FF7E-4656-8007-72B8D4A38612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5662"/>
+  <dimension ref="A1:E5663"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96711,6 +96711,23 @@
         <v>2264</v>
       </c>
     </row>
+    <row r="5663" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5663">
+        <v>616126</v>
+      </c>
+      <c r="B5663">
+        <v>20260725</v>
+      </c>
+      <c r="C5663" s="1">
+        <v>3449</v>
+      </c>
+      <c r="D5663" s="1">
+        <v>1127</v>
+      </c>
+      <c r="E5663" s="1">
+        <v>5661</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E35194D-FF7E-4656-8007-72B8D4A38612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA547C54-170E-4A8C-852C-04BE2FC06940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5663"/>
+  <dimension ref="A1:E5664"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96728,6 +96728,23 @@
         <v>5661</v>
       </c>
     </row>
+    <row r="5664" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5664">
+        <v>616226</v>
+      </c>
+      <c r="B5664">
+        <v>20260726</v>
+      </c>
+      <c r="C5664" s="1">
+        <v>7338</v>
+      </c>
+      <c r="D5664" s="1">
+        <v>9053</v>
+      </c>
+      <c r="E5664" s="1">
+        <v>6235</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA547C54-170E-4A8C-852C-04BE2FC06940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1462E879-000E-42C7-B103-C549060D87B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5664"/>
+  <dimension ref="A1:E5665"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96745,6 +96745,23 @@
         <v>6235</v>
       </c>
     </row>
+    <row r="5665" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5665">
+        <v>616326</v>
+      </c>
+      <c r="B5665">
+        <v>20260728</v>
+      </c>
+      <c r="C5665" s="1">
+        <v>1131</v>
+      </c>
+      <c r="D5665" s="1">
+        <v>3649</v>
+      </c>
+      <c r="E5665" s="1">
+        <v>5515</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1462E879-000E-42C7-B103-C549060D87B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33052B8C-8B87-4F59-9DEA-5764B67A247A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="3168" yWindow="3168" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5665"/>
+  <dimension ref="A1:E5666"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96762,6 +96762,23 @@
         <v>5515</v>
       </c>
     </row>
+    <row r="5666" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5666">
+        <v>616426</v>
+      </c>
+      <c r="B5666">
+        <v>20260729</v>
+      </c>
+      <c r="C5666" s="1">
+        <v>6225</v>
+      </c>
+      <c r="D5666" s="1">
+        <v>4030</v>
+      </c>
+      <c r="E5666" s="1">
+        <v>8017</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33052B8C-8B87-4F59-9DEA-5764B67A247A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3021799F-91B1-477A-BFD1-E1AA9F890DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3168" yWindow="3168" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5666"/>
+  <dimension ref="A1:E5667"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96779,6 +96779,23 @@
         <v>8017</v>
       </c>
     </row>
+    <row r="5667" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5667">
+        <v>616526</v>
+      </c>
+      <c r="B5667">
+        <v>20260801</v>
+      </c>
+      <c r="C5667" s="1">
+        <v>5900</v>
+      </c>
+      <c r="D5667" s="1">
+        <v>6900</v>
+      </c>
+      <c r="E5667" s="1">
+        <v>7415</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3021799F-91B1-477A-BFD1-E1AA9F890DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0215F871-48DF-4BEA-BC0D-218061D02F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3168" yWindow="3168" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5667"/>
+  <dimension ref="A1:E5668"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96796,6 +96796,23 @@
         <v>7415</v>
       </c>
     </row>
+    <row r="5668" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5668">
+        <v>616626</v>
+      </c>
+      <c r="B5668">
+        <v>20260802</v>
+      </c>
+      <c r="C5668" s="1">
+        <v>2759</v>
+      </c>
+      <c r="D5668" s="1">
+        <v>9070</v>
+      </c>
+      <c r="E5668" s="1">
+        <v>6884</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0215F871-48DF-4BEA-BC0D-218061D02F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224A14FA-7DCE-4CE3-9953-50C8EE216E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3168" yWindow="3168" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5668"/>
+  <dimension ref="A1:E5669"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96813,6 +96813,23 @@
         <v>6884</v>
       </c>
     </row>
+    <row r="5669" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5669">
+        <v>616726</v>
+      </c>
+      <c r="B5669">
+        <v>20260805</v>
+      </c>
+      <c r="C5669" s="1">
+        <v>1498</v>
+      </c>
+      <c r="D5669" s="1">
+        <v>6077</v>
+      </c>
+      <c r="E5669" s="1">
+        <v>1943</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224A14FA-7DCE-4CE3-9953-50C8EE216E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C613BA4C-C8E7-46AB-A962-04C89B66BE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5669"/>
+  <dimension ref="A1:E5668"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96813,23 +96813,6 @@
         <v>6884</v>
       </c>
     </row>
-    <row r="5669" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5669">
-        <v>616726</v>
-      </c>
-      <c r="B5669">
-        <v>20260805</v>
-      </c>
-      <c r="C5669" s="1">
-        <v>1498</v>
-      </c>
-      <c r="D5669" s="1">
-        <v>6077</v>
-      </c>
-      <c r="E5669" s="1">
-        <v>1943</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C613BA4C-C8E7-46AB-A962-04C89B66BE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBDEB49-88CA-40AD-818F-1D047B3A4601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5668"/>
+  <dimension ref="A1:E5669"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96813,6 +96813,23 @@
         <v>6884</v>
       </c>
     </row>
+    <row r="5669" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5669">
+        <v>616726</v>
+      </c>
+      <c r="B5669">
+        <v>20260805</v>
+      </c>
+      <c r="C5669" s="1">
+        <v>1498</v>
+      </c>
+      <c r="D5669" s="1">
+        <v>6077</v>
+      </c>
+      <c r="E5669" s="1">
+        <v>1943</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBDEB49-88CA-40AD-818F-1D047B3A4601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFDA162F-E68C-422E-B4E9-E30CBF1E0959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5669"/>
+  <dimension ref="A1:E5668"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96813,23 +96813,6 @@
         <v>6884</v>
       </c>
     </row>
-    <row r="5669" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5669">
-        <v>616726</v>
-      </c>
-      <c r="B5669">
-        <v>20260805</v>
-      </c>
-      <c r="C5669" s="1">
-        <v>1498</v>
-      </c>
-      <c r="D5669" s="1">
-        <v>6077</v>
-      </c>
-      <c r="E5669" s="1">
-        <v>1943</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFDA162F-E68C-422E-B4E9-E30CBF1E0959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5ECEAE7-B4CA-490D-8EE5-EBE8425BD457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5668"/>
+  <dimension ref="A1:E5669"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96813,6 +96813,23 @@
         <v>6884</v>
       </c>
     </row>
+    <row r="5669" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5669">
+        <v>616726</v>
+      </c>
+      <c r="B5669">
+        <v>20260805</v>
+      </c>
+      <c r="C5669" s="1">
+        <v>1498</v>
+      </c>
+      <c r="D5669" s="1">
+        <v>6077</v>
+      </c>
+      <c r="E5669" s="1">
+        <v>1943</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5ECEAE7-B4CA-490D-8EE5-EBE8425BD457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEF5B50-E05B-4739-BA2D-7CFB11AF4F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5669"/>
+  <dimension ref="A1:E5670"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96830,6 +96830,23 @@
         <v>1943</v>
       </c>
     </row>
+    <row r="5670" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5670">
+        <v>616826</v>
+      </c>
+      <c r="B5670">
+        <v>20260808</v>
+      </c>
+      <c r="C5670" s="1">
+        <v>501</v>
+      </c>
+      <c r="D5670" s="1">
+        <v>5324</v>
+      </c>
+      <c r="E5670" s="1">
+        <v>8131</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEF5B50-E05B-4739-BA2D-7CFB11AF4F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4426DB93-3C31-46B1-B8CC-9402992FF011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5670"/>
+  <dimension ref="A1:E5671"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96847,6 +96847,23 @@
         <v>8131</v>
       </c>
     </row>
+    <row r="5671" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5671">
+        <v>616926</v>
+      </c>
+      <c r="B5671">
+        <v>20260809</v>
+      </c>
+      <c r="C5671" s="1">
+        <v>1293</v>
+      </c>
+      <c r="D5671" s="1">
+        <v>4263</v>
+      </c>
+      <c r="E5671" s="1">
+        <v>622</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4426DB93-3C31-46B1-B8CC-9402992FF011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F183DE-FA2C-4480-82E0-FF0B59F0B461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="3036" yWindow="3036" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5671"/>
+  <dimension ref="A1:E5672"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96864,6 +96864,23 @@
         <v>622</v>
       </c>
     </row>
+    <row r="5672" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5672">
+        <v>617026</v>
+      </c>
+      <c r="B5672">
+        <v>20260812</v>
+      </c>
+      <c r="C5672" s="1">
+        <v>2969</v>
+      </c>
+      <c r="D5672" s="1">
+        <v>8440</v>
+      </c>
+      <c r="E5672" s="1">
+        <v>9977</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F183DE-FA2C-4480-82E0-FF0B59F0B461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309E1CA9-8088-4ECE-8AA8-D408C8B07B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3036" yWindow="3036" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5672"/>
+  <dimension ref="A1:E5673"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96881,6 +96881,23 @@
         <v>9977</v>
       </c>
     </row>
+    <row r="5673" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5673">
+        <v>617126</v>
+      </c>
+      <c r="B5673">
+        <v>20260815</v>
+      </c>
+      <c r="C5673" s="1">
+        <v>2976</v>
+      </c>
+      <c r="D5673" s="1">
+        <v>3857</v>
+      </c>
+      <c r="E5673" s="1">
+        <v>2299</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309E1CA9-8088-4ECE-8AA8-D408C8B07B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B864577-DC04-4620-9588-60742AFC6B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5673"/>
+  <dimension ref="A1:E5674"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96898,6 +96898,23 @@
         <v>2299</v>
       </c>
     </row>
+    <row r="5674" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5674">
+        <v>617226</v>
+      </c>
+      <c r="B5674">
+        <v>20260816</v>
+      </c>
+      <c r="C5674" s="1">
+        <v>7582</v>
+      </c>
+      <c r="D5674" s="1">
+        <v>5859</v>
+      </c>
+      <c r="E5674" s="1">
+        <v>7574</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B864577-DC04-4620-9588-60742AFC6B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE76A2BD-2EF8-43BD-B965-35F85AC7A028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5674"/>
+  <dimension ref="A1:E5675"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96915,6 +96915,23 @@
         <v>7574</v>
       </c>
     </row>
+    <row r="5675" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5675">
+        <v>617326</v>
+      </c>
+      <c r="B5675">
+        <v>20260819</v>
+      </c>
+      <c r="C5675" s="1">
+        <v>5691</v>
+      </c>
+      <c r="D5675" s="1">
+        <v>613</v>
+      </c>
+      <c r="E5675" s="1">
+        <v>4868</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE76A2BD-2EF8-43BD-B965-35F85AC7A028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C33B00-BC99-4E6F-940F-3312645EFCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5675"/>
+  <dimension ref="A1:E5676"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96932,6 +96932,23 @@
         <v>4868</v>
       </c>
     </row>
+    <row r="5676" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5676">
+        <v>617426</v>
+      </c>
+      <c r="B5676">
+        <v>20260822</v>
+      </c>
+      <c r="C5676" s="1">
+        <v>7635</v>
+      </c>
+      <c r="D5676" s="1">
+        <v>6320</v>
+      </c>
+      <c r="E5676" s="1">
+        <v>3942</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C33B00-BC99-4E6F-940F-3312645EFCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F68568-3821-4BFB-8373-38A9DA0ACFD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5676"/>
+  <dimension ref="A1:E5677"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96949,6 +96949,23 @@
         <v>3942</v>
       </c>
     </row>
+    <row r="5677" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5677">
+        <v>617526</v>
+      </c>
+      <c r="B5677">
+        <v>20260823</v>
+      </c>
+      <c r="C5677" s="1">
+        <v>1917</v>
+      </c>
+      <c r="D5677" s="1">
+        <v>4489</v>
+      </c>
+      <c r="E5677" s="1">
+        <v>7160</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F68568-3821-4BFB-8373-38A9DA0ACFD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7165B913-E994-49EB-8EAB-BBDADC7C829B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5677"/>
+  <dimension ref="A1:E5678"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96966,6 +96966,23 @@
         <v>7160</v>
       </c>
     </row>
+    <row r="5678" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5678">
+        <v>617626</v>
+      </c>
+      <c r="B5678">
+        <v>20260826</v>
+      </c>
+      <c r="C5678" s="1">
+        <v>6784</v>
+      </c>
+      <c r="D5678" s="1">
+        <v>5201</v>
+      </c>
+      <c r="E5678" s="1">
+        <v>3545</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7165B913-E994-49EB-8EAB-BBDADC7C829B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954115CB-24CE-4E6F-B55C-FF482B5983C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5678"/>
+  <dimension ref="A1:E5679"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -96983,6 +96983,23 @@
         <v>3545</v>
       </c>
     </row>
+    <row r="5679" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5679">
+        <v>617726</v>
+      </c>
+      <c r="B5679">
+        <v>20260829</v>
+      </c>
+      <c r="C5679" s="1">
+        <v>205</v>
+      </c>
+      <c r="D5679" s="1">
+        <v>9039</v>
+      </c>
+      <c r="E5679" s="1">
+        <v>2984</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954115CB-24CE-4E6F-B55C-FF482B5983C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E29CC0-C82A-497F-9F11-6E8C56EB3EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5679"/>
+  <dimension ref="A1:E5680"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97000,6 +97000,23 @@
         <v>2984</v>
       </c>
     </row>
+    <row r="5680" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5680">
+        <v>617826</v>
+      </c>
+      <c r="B5680">
+        <v>20260830</v>
+      </c>
+      <c r="C5680" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D5680" s="1">
+        <v>1164</v>
+      </c>
+      <c r="E5680" s="1">
+        <v>9330</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E29CC0-C82A-497F-9F11-6E8C56EB3EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{670319EE-D008-4EA6-B34D-2FDF538E68D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="2580" yWindow="2580" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5680"/>
+  <dimension ref="A1:E5681"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97017,6 +97017,20 @@
         <v>9330</v>
       </c>
     </row>
+    <row r="5681" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5681">
+        <v>617926</v>
+      </c>
+      <c r="B5681">
+        <v>20260901</v>
+      </c>
+      <c r="C5681" s="1">
+        <v>7855</v>
+      </c>
+      <c r="D5681" s="1">
+        <v>7104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{670319EE-D008-4EA6-B34D-2FDF538E68D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADFA5C0F-CF65-40AF-B7A7-EEC43BF3933D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2580" yWindow="2580" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -97017,7 +97017,7 @@
         <v>9330</v>
       </c>
     </row>
-    <row r="5681" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5681" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5681">
         <v>617926</v>
       </c>
@@ -97029,6 +97029,9 @@
       </c>
       <c r="D5681" s="1">
         <v>7104</v>
+      </c>
+      <c r="E5681" s="1">
+        <v>6735</v>
       </c>
     </row>
   </sheetData>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADFA5C0F-CF65-40AF-B7A7-EEC43BF3933D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0BE982-524F-478D-8B34-9B739A56EC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2580" yWindow="2580" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5681"/>
+  <dimension ref="A1:E5682"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97034,6 +97034,23 @@
         <v>6735</v>
       </c>
     </row>
+    <row r="5682" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5682">
+        <v>618026</v>
+      </c>
+      <c r="B5682">
+        <v>20260902</v>
+      </c>
+      <c r="C5682" s="1">
+        <v>4660</v>
+      </c>
+      <c r="D5682" s="1">
+        <v>6655</v>
+      </c>
+      <c r="E5682" s="1">
+        <v>8808</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0BE982-524F-478D-8B34-9B739A56EC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1AA1E2-0BEC-4E6F-BE6C-680BB3BABE85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="2580" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5682"/>
+  <dimension ref="A1:E5683"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97051,6 +97051,23 @@
         <v>8808</v>
       </c>
     </row>
+    <row r="5683" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5683">
+        <v>618126</v>
+      </c>
+      <c r="B5683">
+        <v>20260905</v>
+      </c>
+      <c r="C5683" s="1">
+        <v>3595</v>
+      </c>
+      <c r="D5683" s="1">
+        <v>4754</v>
+      </c>
+      <c r="E5683" s="1">
+        <v>9379</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1AA1E2-0BEC-4E6F-BE6C-680BB3BABE85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAF8FBD-06B2-485F-B4FB-18795A72A102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5683"/>
+  <dimension ref="A1:E5684"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97068,6 +97068,23 @@
         <v>9379</v>
       </c>
     </row>
+    <row r="5684" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5684">
+        <v>618226</v>
+      </c>
+      <c r="B5684">
+        <v>20260906</v>
+      </c>
+      <c r="C5684" s="1">
+        <v>9616</v>
+      </c>
+      <c r="D5684" s="1">
+        <v>3927</v>
+      </c>
+      <c r="E5684" s="1">
+        <v>6628</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAF8FBD-06B2-485F-B4FB-18795A72A102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF100EF-9CA9-4BCD-A31E-CEC294EDAD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5684"/>
+  <dimension ref="A1:E5685"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97085,6 +97085,23 @@
         <v>6628</v>
       </c>
     </row>
+    <row r="5685" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5685">
+        <v>618326</v>
+      </c>
+      <c r="B5685">
+        <v>20260909</v>
+      </c>
+      <c r="C5685" s="1">
+        <v>7253</v>
+      </c>
+      <c r="D5685" s="1">
+        <v>1994</v>
+      </c>
+      <c r="E5685" s="1">
+        <v>6332</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
